--- a/testing/TEST_EXECUTION_RESULTS.xlsx
+++ b/testing/TEST_EXECUTION_RESULTS.xlsx
@@ -463,18 +463,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1746,6 +1746,194 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>EXE-027</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>TC-AUTH-009</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Legitimate Email Enforcement</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Security/UI</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Chrome / API</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Arbitrary emails blocked with clear error messaging</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Regex and DNS domain validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>EXE-028</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>TC-AUTH-010</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Mandatory Email OTP</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Gmail SMTP / Redis</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>6-digit OTP delivered and verified in login &amp; signup</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>SMTP and cache functional</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>EXE-029</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>TC-STAT-001</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Clean Zero-State Initialization</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>React / Postgres</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>New users start with 0-day streak and blank stats</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Zero phantom statistics</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>EXE-030</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>TC-SEL-001</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Selenium E2E Test Suite</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Automated E2E</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Headless Chrome</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>All 8 Selenium test suites passed with 8 screenshots</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100% E2E automated pass</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
